--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486274_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486274_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6436</v>
+        <v>5.1717</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1023</v>
+        <v>3.5687</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5414</v>
+        <v>1.603</v>
       </c>
       <c r="G2" t="n">
         <v>1.2964</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5446</v>
+        <v>0.0727</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8736</v>
+        <v>0.3401</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.329</v>
+        <v>-0.2674</v>
       </c>
       <c r="V2" t="n">
         <v>3.5851</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4277</v>
+        <v>4.7785</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7902</v>
+        <v>3.7095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6375999999999999</v>
+        <v>1.0691</v>
       </c>
       <c r="G3" t="n">
         <v>4.335</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3598</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8784</v>
+        <v>0.0409</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4814</v>
+        <v>-0.0499</v>
       </c>
       <c r="V3" t="n">
         <v>4.1501</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4947</v>
+        <v>3.0834</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9436</v>
+        <v>3.3473</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4489</v>
+        <v>-0.2639</v>
       </c>
       <c r="G4" t="n">
         <v>4.9534</v>
@@ -766,13 +766,13 @@
         <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2863</v>
+        <v>-0.6976</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.548</v>
+        <v>-0.1442</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7383</v>
+        <v>-0.5534</v>
       </c>
       <c r="V4" t="n">
         <v>-2.2599</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6112</v>
+        <v>1.7375</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5127</v>
+        <v>1.9165</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0985</v>
+        <v>-0.1789</v>
       </c>
       <c r="G5" t="n">
         <v>2.1706</v>
@@ -844,13 +844,13 @@
         <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0395</v>
+        <v>0.0868</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3425</v>
+        <v>0.0613</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3029</v>
+        <v>0.0255</v>
       </c>
       <c r="V5" t="n">
         <v>-2.2599</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0225</v>
+        <v>0.4089</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0429</v>
+        <v>0.5526</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0204</v>
+        <v>-0.1437</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3424</v>
@@ -922,13 +922,13 @@
         <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5823</v>
+        <v>-0.0312</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5432</v>
+        <v>0.0529</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0392</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1442</v>
+        <v>-0.0757</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3682</v>
+        <v>0.4367</v>
       </c>
       <c r="F7" t="n">
         <v>-0.5125</v>
@@ -1000,10 +1000,10 @@
         <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.423</v>
+        <v>-0.3545</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.274</v>
+        <v>-0.2055</v>
       </c>
       <c r="U7" t="n">
         <v>-0.149</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6936</v>
+        <v>-0.2428</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.8733</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4551</v>
+        <v>-1.1161</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4325</v>
@@ -1078,13 +1078,13 @@
         <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.216</v>
+        <v>-0.7652</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5995</v>
+        <v>-0.2605</v>
       </c>
       <c r="V8" t="n">
         <v>2.2599</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.479</v>
+        <v>-2.0143</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7185</v>
+        <v>-0.63</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2395</v>
+        <v>-1.3844</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4104</v>
+        <v>-1.8161</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.3819</v>
+        <v>-4.3948</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9714</v>
+        <v>2.5786</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5233</v>
+        <v>-0.9265</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1735</v>
+        <v>-2.2685</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6502</v>
+        <v>1.342</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8872</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.2083</v>
+        <v>-2.1263</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3212</v>
+        <v>1.2367</v>
       </c>
       <c r="P9" t="n">
+        <v>0.2175</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.305</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-2.3926</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6508</v>
+        <v>-0.2205</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6117</v>
+        <v>0.2764</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0392</v>
+        <v>-0.4969</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5857</v>
+        <v>-0.1952</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5857</v>
+        <v>1.3252</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8777</v>
+        <v>-2.0521</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4317</v>
+        <v>-0.2833</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.446</v>
+        <v>-1.7688</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8161</v>
+        <v>-0.1535</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.3948</v>
+        <v>-0.8061</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5786</v>
+        <v>0.6526</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9265</v>
+        <v>1.6277</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2685</v>
+        <v>1.5512</v>
       </c>
       <c r="L10" t="n">
-        <v>1.342</v>
+        <v>0.0765</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-1.7812</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.1263</v>
+        <v>-2.3573</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2367</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2175</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.305</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0839</v>
+        <v>0.3836</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4747</v>
+        <v>-0.4314</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5586</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1952</v>
+        <v>-2.0647</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3252</v>
+        <v>-0.1745</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5204</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0984</v>
+        <v>-2.1611</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-2.2773</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3681</v>
+        <v>0.1163</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1535</v>
+        <v>-1.4104</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8061</v>
+        <v>-3.3819</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6526</v>
+        <v>1.9714</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6277</v>
+        <v>-0.5233</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5512</v>
+        <v>-1.1735</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0765</v>
+        <v>0.6502</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7812</v>
+        <v>-0.8872</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.3573</v>
+        <v>-2.2083</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5760999999999999</v>
+        <v>1.3212</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R11" t="n">
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3373</v>
+        <v>-0.0312</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8784</v>
+        <v>0.0529</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2157</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.0647</v>
+        <v>0.5857</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.1745</v>
+        <v>0.5857</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3753</v>
+        <v>-4.4176</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2559</v>
+        <v>-4.1442</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1193</v>
+        <v>-0.2735</v>
       </c>
       <c r="G12" t="n">
         <v>-0.008699999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3443</v>
+        <v>-0.3866</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1352</v>
+        <v>-0.0189</v>
       </c>
       <c r="V12" t="n">
         <v>-2.0647</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.531500000000002</v>
+        <v>4.216400000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>6.385100000000002</v>
+        <v>7.069799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8533</v>
+        <v>-2.8534</v>
       </c>
       <c r="G13" t="n">
-        <v>7.6531</v>
+        <v>7.653100000000002</v>
       </c>
       <c r="H13" t="n">
         <v>-13.1848</v>
       </c>
       <c r="I13" t="n">
-        <v>20.83769999999999</v>
+        <v>20.8377</v>
       </c>
       <c r="J13" t="n">
         <v>16.7674</v>
@@ -1468,13 +1468,13 @@
         <v>17.4006</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.6378</v>
+        <v>-1.9527</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5141</v>
+        <v>-0.829</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1236</v>
+        <v>-1.1237</v>
       </c>
       <c r="V13" t="n">
         <v>2.866400000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.562</v>
+        <v>3.4882</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6604</v>
+        <v>0.5911</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0984</v>
+        <v>2.8971</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6237</v>
+        <v>1.6671</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0078</v>
+        <v>1.8886</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3841</v>
+        <v>-0.2215</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0494</v>
+        <v>1.7564</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0111</v>
+        <v>1.2775</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0382</v>
+        <v>0.4789</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4257</v>
+        <v>-0.0893</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0033</v>
+        <v>0.6111</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4224</v>
+        <v>-0.7004</v>
       </c>
       <c r="P14" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1335</v>
+        <v>0.1691</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0036</v>
+        <v>-0.1202</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1299</v>
+        <v>0.2893</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3698</v>
+        <v>1.8695</v>
       </c>
       <c r="W14" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3252</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1221</v>
+        <v>3.4336</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2558</v>
+        <v>3.6604</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8662</v>
+        <v>-0.2268</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6671</v>
+        <v>2.6237</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8886</v>
+        <v>3.0078</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2215</v>
+        <v>-0.3841</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7564</v>
+        <v>3.0494</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2775</v>
+        <v>3.0111</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4789</v>
+        <v>0.0382</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0893</v>
+        <v>-0.4257</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6111</v>
+        <v>-0.0033</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7004</v>
+        <v>-0.4224</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.197</v>
+        <v>0.0051</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4554</v>
+        <v>0.0036</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2585</v>
+        <v>0.0015</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8695</v>
+        <v>0.3698</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7395</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.281</v>
+        <v>1.5238</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4192</v>
+        <v>1.7544</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1382</v>
+        <v>-0.2307</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5084</v>
@@ -1702,13 +1702,13 @@
         <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2107</v>
+        <v>0.0321</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4554</v>
+        <v>-0.1202</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2448</v>
+        <v>0.1523</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.8542</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8098</v>
+        <v>-1.5863</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5946</v>
+        <v>2.4405</v>
       </c>
       <c r="G17" t="n">
         <v>0.4853</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0703</v>
+        <v>-0.0009</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4777</v>
+        <v>0.3235</v>
       </c>
       <c r="V17" t="n">
         <v>0.3698</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.279</v>
+        <v>0.744</v>
       </c>
       <c r="E18" t="n">
-        <v>4.141</v>
+        <v>4.3645</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.862</v>
+        <v>-3.6205</v>
       </c>
       <c r="G18" t="n">
         <v>-1.699</v>
@@ -1858,13 +1858,13 @@
         <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3032</v>
+        <v>0.7682</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3581</v>
+        <v>0.5816</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0549</v>
+        <v>0.1866</v>
       </c>
       <c r="V18" t="n">
         <v>0.3698</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7209</v>
+        <v>-0.4971</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8419</v>
+        <v>-1.3164</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5628</v>
+        <v>0.8194</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1086</v>
+        <v>-4.65</v>
       </c>
       <c r="H19" t="n">
-        <v>2.208</v>
+        <v>-0.955</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.3166</v>
+        <v>-3.695</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5713</v>
+        <v>-2.2377</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4089</v>
+        <v>0.2253</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.9802</v>
+        <v>-2.463</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5372</v>
+        <v>-2.4123</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2009</v>
+        <v>-1.1803</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3364</v>
+        <v>-1.232</v>
       </c>
       <c r="P19" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>2.8276</v>
       </c>
       <c r="S19" t="n">
-        <v>1.038</v>
+        <v>0.3704</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6307</v>
+        <v>-0.0336</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5927</v>
+        <v>0.4041</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9554</v>
+        <v>2.2599</v>
       </c>
       <c r="W19" t="n">
+        <v>2.2599</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.9554</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9649</v>
+        <v>-1.5388</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7086</v>
+        <v>-2.7734</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6735</v>
+        <v>1.2346</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4285</v>
+        <v>-5.4135</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8668</v>
+        <v>-2.7217</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5618</v>
+        <v>-2.6918</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4192</v>
+        <v>-3.5312</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7546</v>
+        <v>-2.1558</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6647</v>
+        <v>-1.3754</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9907</v>
+        <v>-1.8823</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1122</v>
+        <v>-0.5659</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1029</v>
+        <v>-1.3164</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5225</v>
+        <v>2.3926</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2626</v>
+        <v>-0.435</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7401</v>
+        <v>2.8276</v>
       </c>
       <c r="S20" t="n">
-        <v>1.389</v>
+        <v>0.7219</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3567</v>
+        <v>0.4326</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0323</v>
+        <v>0.2893</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2599</v>
+        <v>0.7602</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2716</v>
+        <v>-1.5547</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8752</v>
+        <v>-0.3874</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6036</v>
+        <v>-1.1672</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.65</v>
+        <v>-2.1086</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.955</v>
+        <v>2.208</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.695</v>
+        <v>-4.3166</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.2377</v>
+        <v>-0.5713</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2253</v>
+        <v>2.4089</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.463</v>
+        <v>-2.9802</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4123</v>
+        <v>-1.5372</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1803</v>
+        <v>-0.2009</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.232</v>
+        <v>-1.3364</v>
       </c>
       <c r="P21" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.5225</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.305</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.8276</v>
-      </c>
       <c r="S21" t="n">
-        <v>-0.4041</v>
+        <v>0.2043</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5924</v>
+        <v>0.4014</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1883</v>
+        <v>-0.1971</v>
       </c>
       <c r="V21" t="n">
-        <v>2.2599</v>
+        <v>-0.9554</v>
       </c>
       <c r="W21" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5465</v>
+        <v>-1.8525</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9969</v>
+        <v>-0.2973</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4503</v>
+        <v>-1.5553</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.4135</v>
+        <v>1.4285</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7217</v>
+        <v>0.8668</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.6918</v>
+        <v>0.5618</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.5312</v>
+        <v>2.4192</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.1558</v>
+        <v>0.7546</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3754</v>
+        <v>1.6647</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8823</v>
+        <v>-0.9907</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5659</v>
+        <v>0.1122</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3164</v>
+        <v>-1.1029</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3926</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.435</v>
+        <v>-3.2626</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8276</v>
+        <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.5014</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2091</v>
+        <v>0.3509</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5051</v>
+        <v>0.1505</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7602</v>
+        <v>-2.2599</v>
       </c>
       <c r="W22" t="n">
-        <v>0.7602</v>
+        <v>0.1952</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2152</v>
+        <v>-2.2589</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9117</v>
+        <v>0.6882</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1269</v>
+        <v>-2.9471</v>
       </c>
       <c r="G23" t="n">
         <v>1.3754</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3871</v>
+        <v>0.3434</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3581</v>
+        <v>0.1346</v>
       </c>
       <c r="U23" t="n">
-        <v>0.029</v>
+        <v>0.2088</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4552</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8411</v>
+        <v>-5.1282</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4032</v>
+        <v>-1.8444</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4379</v>
+        <v>-3.2838</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8537</v>
@@ -2326,13 +2326,13 @@
         <v>3.4801</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4452</v>
+        <v>0.2677</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.1826</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2962</v>
+        <v>0.4503</v>
       </c>
       <c r="V24" t="n">
         <v>-4.3247</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.531299999999999</v>
+        <v>-2.786399999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>2.853499999999999</v>
+        <v>2.8534</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.385</v>
+        <v>-5.639799999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-7.653200000000001</v>
@@ -2404,13 +2404,13 @@
         <v>21.7507</v>
       </c>
       <c r="S25" t="n">
-        <v>2.637700000000001</v>
+        <v>3.3827</v>
       </c>
       <c r="T25" t="n">
-        <v>1.1237</v>
+        <v>1.1236</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5142</v>
+        <v>2.2591</v>
       </c>
       <c r="V25" t="n">
         <v>-2.8662</v>
